--- a/Pruebas calificadas/COLEGIO-BRASILIA-USME-(IED)-301_Ajustado_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-BRASILIA-USME-(IED)-301_Ajustado_CALIFICADO.xlsx
@@ -747,11 +747,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -759,7 +755,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -946,11 +942,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -958,7 +950,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1145,11 +1137,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -1157,7 +1145,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1344,11 +1332,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -1356,7 +1340,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1547,11 +1531,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -1559,7 +1539,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1746,11 +1726,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -1758,7 +1734,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1941,11 +1917,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -1953,7 +1925,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2140,11 +2112,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -2152,7 +2120,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2339,11 +2307,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -2351,7 +2315,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2542,11 +2506,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -2554,7 +2514,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2745,11 +2705,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -2757,7 +2713,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2944,11 +2900,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -2956,7 +2908,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3143,11 +3095,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -3155,7 +3103,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -3346,11 +3294,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -3358,7 +3302,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -3549,11 +3493,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -3561,7 +3501,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3752,11 +3692,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -3764,7 +3700,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3955,11 +3891,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -3967,7 +3899,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -4158,11 +4090,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -4170,7 +4098,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -4361,11 +4289,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -4373,7 +4297,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -4564,11 +4488,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -4576,7 +4496,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -4767,11 +4687,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -4779,7 +4695,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -4970,11 +4886,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -4982,7 +4894,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -5173,11 +5085,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -5185,7 +5093,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -5376,11 +5284,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -5388,7 +5292,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -5579,11 +5483,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -5591,7 +5491,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -5782,11 +5682,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -5794,7 +5690,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -5981,11 +5877,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -5993,7 +5885,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -6184,11 +6076,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -6196,7 +6084,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -6387,11 +6275,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -6399,7 +6283,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -6586,11 +6470,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -6598,7 +6478,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -6785,11 +6665,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -6797,7 +6673,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -6988,11 +6864,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -7000,7 +6872,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -7191,11 +7063,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -7203,7 +7071,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -7394,11 +7262,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -7406,7 +7270,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -7597,11 +7461,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -7609,7 +7469,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -7800,11 +7660,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -7812,7 +7668,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -8003,11 +7859,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -8015,7 +7867,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -8206,11 +8058,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -8218,7 +8066,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -8409,11 +8257,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -8421,7 +8265,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -8612,11 +8456,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -8624,7 +8464,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -8815,11 +8655,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -8827,7 +8663,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -9014,11 +8850,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -9026,7 +8858,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -9217,11 +9049,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -9229,7 +9057,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -9420,11 +9248,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -9432,7 +9256,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -9623,11 +9447,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -9635,7 +9455,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -9826,11 +9646,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001077917</t>
@@ -9838,7 +9654,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO BRASILIA - USME (IED)</t>
+          <t>COLEGIO BRASILIA - USME</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
